--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>47061.04</v>
+        <v>46536.71</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>28758.98</v>
+        <v>28966.32</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>25856.53</v>
+        <v>25816.45</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>154308.04</v>
+        <v>153974.09</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>49950.28</v>
+        <v>49842.18</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75905.71000000001</v>
+        <v>75741.44</v>
       </c>
     </row>
     <row r="9">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>146476.45</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>47201.86</v>
+        <v>47099.71</v>
       </c>
     </row>
     <row r="11">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>246210.53</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="12">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26407.84</v>
+        <v>26184.15</v>
       </c>
     </row>
     <row r="13">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18107.51</v>
+        <v>18232.15</v>
       </c>
     </row>
     <row r="14">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>148074.09</v>
+        <v>148883.86</v>
       </c>
     </row>
     <row r="15">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>46345.79</v>
+        <v>45998.94</v>
       </c>
     </row>
     <row r="16">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27293.16</v>
+        <v>27483.18</v>
       </c>
     </row>
     <row r="17">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>37769.48</v>
+        <v>37802.01</v>
       </c>
     </row>
     <row r="18">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25993.05</v>
+        <v>25921.35</v>
       </c>
     </row>
     <row r="19">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38269.33</v>
+        <v>37827.53</v>
       </c>
     </row>
     <row r="20">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38513.08</v>
+        <v>37938.64</v>
       </c>
     </row>
     <row r="21">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>76642.48</v>
+        <v>75499.33</v>
       </c>
     </row>
     <row r="22">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>43907.35</v>
+        <v>42962.68</v>
       </c>
     </row>
     <row r="23">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>52413.84</v>
+        <v>51194.22</v>
       </c>
     </row>
     <row r="24">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21620.48</v>
+        <v>21051.14</v>
       </c>
     </row>
     <row r="25">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>39677.35</v>
+        <v>40195.13</v>
       </c>
     </row>
     <row r="26">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>23562.73</v>
+        <v>23503.24</v>
       </c>
     </row>
     <row r="27">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>78587.59</v>
+        <v>78409.21000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14650.23</v>
+        <v>14698.83</v>
       </c>
     </row>
     <row r="29">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>38791.81</v>
+        <v>38915.28</v>
       </c>
     </row>
     <row r="30">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>39581.29</v>
+        <v>39707.27</v>
       </c>
     </row>
     <row r="31">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>34762.19</v>
+        <v>35169.97</v>
       </c>
     </row>
     <row r="32">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>22138.97</v>
+        <v>21971.02</v>
       </c>
     </row>
     <row r="33">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14247.32</v>
+        <v>14045.11</v>
       </c>
     </row>
     <row r="34">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>67725.33</v>
+        <v>66794.75999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17771.27</v>
+        <v>18109.13</v>
       </c>
     </row>
     <row r="36">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>14647.21</v>
+        <v>14692.49</v>
       </c>
     </row>
     <row r="37">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>37402.92</v>
+        <v>37548.93</v>
       </c>
     </row>
     <row r="38">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>761.21</v>
+        <v>764.1799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3153-368-CM25</t>
+          <t>765-253-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>46536.71</v>
+        <v>26180.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3434-120-CM25</t>
+          <t>3938-266-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>28966.32</v>
+        <v>34597.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2546-995-CM25</t>
+          <t>3153-368-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>25816.45</v>
+        <v>46536.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3290-353-CM25</t>
+          <t>3434-120-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Carabineros de Chile - IX Zona Araucania</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>42056.86</v>
+        <v>28966.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1001-280-SE25</t>
+          <t>2546-995-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,32 +798,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EQUIPOS Y CAMIONES SPA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.517.323-8</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>153974.09</v>
+        <v>25816.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1001-279-CM25</t>
+          <t>3290-353-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -838,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,32 +859,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>49842.18</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4284-589-CM25</t>
+          <t>1001-280-SE25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -913,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,28 +920,32 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>EQUIPOS Y CAMIONES SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>77.517.323-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75741.44</v>
+        <v>153974.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1001-275-CM25</t>
+          <t>4284-589-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -974,12 +970,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,32 +985,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>146159.45</v>
+        <v>75741.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2548-949-CM25</t>
+          <t>1001-277-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1039,12 +1031,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1054,28 +1046,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>47099.71</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1001-277-CM25</t>
+          <t>1001-275-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1115,17 +1111,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1134,13 +1130,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>245677.7</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1001-295-CM25</t>
+          <t>2548-949-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1155,7 +1151,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1165,12 +1161,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1195,13 +1191,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>26184.15</v>
+        <v>47099.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3937-485-CM25</t>
+          <t>1001-279-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,7 +1212,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1226,12 +1222,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1241,28 +1237,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18232.15</v>
+        <v>49842.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3935-300-CM25</t>
+          <t>1001-295-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1302,32 +1302,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>148883.86</v>
+        <v>26184.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4170-27-CM26</t>
+          <t>3937-485-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1337,27 +1333,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1367,12 +1363,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1382,13 +1378,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>45998.94</v>
+        <v>18232.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2745-17-CM26</t>
+          <t>3935-300-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1398,27 +1394,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1428,28 +1424,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>27483.18</v>
+        <v>148883.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4406-234-CM26</t>
+          <t>4170-27-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1459,27 +1459,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>I MUNICIPALIDAD DE GALVARINO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>37802.01</v>
+        <v>45998.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3608-153-CM26</t>
+          <t>2745-17-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1520,27 +1520,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25921.35</v>
+        <v>27483.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3477-221-CM26</t>
+          <t>4406-234-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LUMACO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>37827.53</v>
+        <v>37802.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4281-60-CM26</t>
+          <t>3608-153-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>37938.64</v>
+        <v>25921.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2057-34-CM26</t>
+          <t>3477-221-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>75499.33</v>
+        <v>37827.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3151-187-CM26</t>
+          <t>2057-34-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>42962.68</v>
+        <v>75499.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3565-187-CM26</t>
+          <t>4281-60-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.252.100-5</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1870,43 +1870,43 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>51194.22</v>
+        <v>37938.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1658-853-CM26</t>
+          <t>3151-187-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1931,43 +1931,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21051.14</v>
+        <v>42962.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3495-79-CM26</t>
+          <t>3565-187-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.252.100-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>40195.13</v>
+        <v>51194.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3705-225-CM26</t>
+          <t>1658-853-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,27 +2008,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>23503.24</v>
+        <v>21051.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3587-172-CM26</t>
+          <t>3495-79-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.190.500-4</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARAHUE</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>78409.21000000001</v>
+        <v>40195.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3799-175-CM26</t>
+          <t>3705-225-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14698.83</v>
+        <v>23503.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3938-173-CM26</t>
+          <t>3587-172-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2236,13 +2236,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>38915.28</v>
+        <v>78409.21000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4993-261-CM26</t>
+          <t>3799-175-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>39707.27</v>
+        <v>14698.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3153-167-CM26</t>
+          <t>3938-173-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2358,13 +2358,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>35169.97</v>
+        <v>38915.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3200-212-CM26</t>
+          <t>4993-261-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.265.000-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2419,13 +2419,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>21971.02</v>
+        <v>39707.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3705-279-CM26</t>
+          <t>3153-167-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2480,13 +2480,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14045.11</v>
+        <v>35169.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4179-672-CM26</t>
+          <t>3200-212-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2501,22 +2501,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>66794.75999999999</v>
+        <v>21971.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3502-259-CM26</t>
+          <t>3705-279-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18109.13</v>
+        <v>14045.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3887-225-CM26</t>
+          <t>4179-672-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2623,22 +2623,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>14692.49</v>
+        <v>66794.75999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4993-351-CM26</t>
+          <t>3502-259-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>37548.93</v>
+        <v>18109.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4993-352-CM26</t>
+          <t>3887-225-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2785,6 +2785,128 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
+        <v>14692.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4993-351-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.265.000-k</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>37548.93</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4993-352-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.265.000-k</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>764.1799999999999</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>765-253-CM25</t>
+          <t>707423-11-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26180.9</v>
+        <v>24518.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3938-266-CM25</t>
+          <t>1658-1959-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34597.33</v>
+        <v>24532.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3153-368-CM25</t>
+          <t>2387-119-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>46536.71</v>
+        <v>80167.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3434-120-CM25</t>
+          <t>4050-155-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>28966.32</v>
+        <v>32339.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2546-995-CM25</t>
+          <t>3608-159-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>25816.45</v>
+        <v>43574.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3290-353-CM25</t>
+          <t>1426099-58-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>42056.86</v>
+        <v>29558.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1001-280-SE25</t>
+          <t>1426099-66-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,32 +920,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EQUIPOS Y CAMIONES SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.517.323-8</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>153974.09</v>
+        <v>25556.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4284-589-CM25</t>
+          <t>1207-1-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>75741.44</v>
+        <v>35109.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1001-277-CM25</t>
+          <t>3836-293-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,17 +1042,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1065,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>245677.7</v>
+        <v>179118.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1001-275-CM25</t>
+          <t>3935-68-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1081,12 +1077,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1096,12 +1092,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1111,32 +1107,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>146159.45</v>
+        <v>27447.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2548-949-CM25</t>
+          <t>4050-266-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1146,27 +1138,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1176,7 +1168,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1191,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>47099.71</v>
+        <v>49766.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1001-279-CM25</t>
+          <t>4513-54-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1207,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1222,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1237,32 +1229,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>49842.18</v>
+        <v>36123.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1001-295-CM25</t>
+          <t>3516-347-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1272,27 +1260,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1302,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1317,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>26184.15</v>
+        <v>18451.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3937-485-CM25</t>
+          <t>4170-134-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1333,27 +1321,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1378,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>18232.15</v>
+        <v>69847.46000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3935-300-CM25</t>
+          <t>4179-1300-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1394,27 +1382,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1424,32 +1412,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>148883.86</v>
+        <v>36584.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4170-27-CM26</t>
+          <t>2389-300-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1459,27 +1443,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1489,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1504,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>45998.94</v>
+        <v>36697.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2745-17-CM26</t>
+          <t>2546-454-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1520,27 +1504,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1550,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1565,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27483.18</v>
+        <v>19700.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4406-234-CM26</t>
+          <t>3587-148-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1581,27 +1565,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1611,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1626,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>37802.01</v>
+        <v>36781.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3608-153-CM26</t>
+          <t>3937-205-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1642,12 +1626,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1657,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1672,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1687,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>25921.35</v>
+        <v>35533.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3477-221-CM26</t>
+          <t>765-253-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1703,12 +1687,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1718,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1733,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1748,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>37827.53</v>
+        <v>26180.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2057-34-CM26</t>
+          <t>1685-88-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1764,27 +1748,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1794,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1809,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>75499.33</v>
+        <v>29185.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4281-60-CM26</t>
+          <t>1685-89-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1825,27 +1809,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1855,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1870,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>37938.64</v>
+        <v>33854.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3151-187-CM26</t>
+          <t>2546-641-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1886,12 +1870,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1901,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1916,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1931,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>42962.68</v>
+        <v>25288.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3565-187-CM26</t>
+          <t>3938-266-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1947,27 +1931,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.252.100-5</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1977,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1992,43 +1976,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>51194.22</v>
+        <v>34597.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1658-853-CM26</t>
+          <t>2389-514-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2038,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2053,28 +2037,28 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>21051.14</v>
+        <v>33435.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3495-79-CM26</t>
+          <t>3477-493-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2099,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2114,43 +2098,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>40195.13</v>
+        <v>39448.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3705-225-CM26</t>
+          <t>3495-176-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2160,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2175,43 +2159,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>23503.24</v>
+        <v>34680.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3587-172-CM26</t>
+          <t>4513-112-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.190.500-4</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARAHUE</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2221,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2236,28 +2220,28 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>78409.21000000001</v>
+        <v>84008.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3799-175-CM26</t>
+          <t>722-172-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2267,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2282,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2297,43 +2281,43 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>14698.83</v>
+        <v>51382.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3938-173-CM26</t>
+          <t>1658-4733-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2343,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2358,28 +2342,28 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>38915.28</v>
+        <v>22931.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4993-261-CM26</t>
+          <t>655-2287-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2389,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>61.821.000-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2404,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2419,43 +2403,43 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>39707.27</v>
+        <v>51992.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3153-167-CM26</t>
+          <t>1148-105-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2465,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2480,43 +2464,43 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>35169.97</v>
+        <v>26801.81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3200-212-CM26</t>
+          <t>3434-115-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2526,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2541,28 +2525,28 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>21971.02</v>
+        <v>24601.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3705-279-CM26</t>
+          <t>3153-368-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2572,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2587,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2602,28 +2586,28 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14045.11</v>
+        <v>46536.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4179-672-CM26</t>
+          <t>3434-120-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2633,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>Carabineros de Chile - IX Zona Araucania</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2648,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2663,28 +2647,28 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>66794.75999999999</v>
+        <v>28966.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3502-259-CM26</t>
+          <t>2546-995-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2694,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2709,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2724,43 +2708,43 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>18109.13</v>
+        <v>25816.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3887-225-CM26</t>
+          <t>3290-353-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2770,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2785,28 +2769,28 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>14692.49</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4993-351-CM26</t>
+          <t>4284-589-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2816,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2831,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2846,68 +2830,2345 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>37548.93</v>
+        <v>75741.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>1001-280-SE25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EQUIPOS Y CAMIONES SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.517.323-8</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>153974.09</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1001-279-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>49842.18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1001-277-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>245677.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1001-275-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>146159.45</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2548-949-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>47099.71</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1001-295-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>26184.15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3937-485-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.252.400-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>18232.15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3935-300-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>148883.86</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4170-27-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE GALVARINO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>45998.94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2745-17-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>27483.18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4406-234-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.180.800-9</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LUMACO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>37802.01</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3608-153-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.190.600-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>25921.35</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3477-221-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>37827.53</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4281-60-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>37938.64</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2057-34-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>75499.33</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3151-187-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.191.100-4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>42962.68</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3565-187-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.252.100-5</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>51194.22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1658-853-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>21051.14</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3495-79-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>40195.13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3705-225-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>23503.24</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3587-172-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.190.500-4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>78409.21000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3799-175-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.180.200-0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUREN</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>14698.83</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4993-261-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.265.000-k</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>39707.27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3938-173-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.252.400-4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>38915.28</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3153-167-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.180.500-k</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>35169.97</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3200-212-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.191.100-4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>21971.02</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3705-279-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>14045.11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4179-672-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>66794.75999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3502-259-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>18109.13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3887-225-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>14692.49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4993-351-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.265.000-k</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>37548.93</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>4993-352-CM26</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>69.265.000-k</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n">
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
         <v>764.1799999999999</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2387-364-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>72037.42999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4118-31-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>27195.83</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4118-32-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>59679.82</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4125-110-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>70.766.500-9</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>38588.16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4177-100-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>25368.27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3887-303-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>25838.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1799,7 +1799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1685-89-CM25</t>
+          <t>2546-641-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>33854.64</v>
+        <v>25288.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2546-641-CM25</t>
+          <t>1685-89-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25288.98</v>
+        <v>33854.64</v>
       </c>
     </row>
     <row r="25">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4281-60-CM26</t>
+          <t>2057-34-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>37938.64</v>
+        <v>75499.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2057-34-CM26</t>
+          <t>4281-60-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>75499.33</v>
+        <v>37938.64</v>
       </c>
     </row>
     <row r="55">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4991,7 +4991,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4125-110-CM26</t>
+          <t>4177-100-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5046,13 +5046,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>38588.16</v>
+        <v>25368.27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4177-100-CM26</t>
+          <t>4125-110-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5072,17 +5072,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>70.766.500-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>25368.27</v>
+        <v>38588.16</v>
       </c>
     </row>
     <row r="77">
@@ -5169,6 +5169,254 @@
       </c>
       <c r="M77" s="2" t="n">
         <v>25838.53</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>3516-570-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.190.500-4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>34156.65</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2548-545-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>44008.37</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>655-136-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.821.000-6</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>59227.84</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4170-270-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.190.200-5</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Galvarino</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>94828.49000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -562,7 +562,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1862,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1927,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1992,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2057,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2122,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2187,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2252,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2317,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2382,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2447,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2512,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2577,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2642,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2707,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2772,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2837,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2902,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2967,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3144,7 +3292,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3205,7 +3357,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3266,7 +3422,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3392,7 +3552,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3453,7 +3617,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3514,7 +3682,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3575,7 +3747,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3636,7 +3812,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3697,7 +3877,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3758,7 +3942,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3819,7 +4007,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3880,7 +4072,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3941,7 +4137,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4002,7 +4202,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4063,7 +4267,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4124,7 +4332,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4185,7 +4397,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4246,7 +4462,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4307,7 +4527,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4429,7 +4653,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4490,7 +4718,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4612,7 +4844,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4734,7 +4970,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4795,7 +5035,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4856,7 +5100,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5100,7 +5348,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5161,7 +5413,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5283,7 +5539,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -5226,7 +5226,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1879,7 +1879,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2546-641-CM25</t>
+          <t>1685-89-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>25288.98</v>
+        <v>33854.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1685-89-CM25</t>
+          <t>2546-641-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>33854.64</v>
+        <v>25288.98</v>
       </c>
     </row>
     <row r="25">
@@ -4414,7 +4414,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4993-261-CM26</t>
+          <t>3938-173-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>39707.27</v>
+        <v>38915.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3938-173-CM26</t>
+          <t>4993-261-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.265.000-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>38915.28</v>
+        <v>39707.27</v>
       </c>
     </row>
     <row r="64">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5681,6 +5681,266 @@
       </c>
       <c r="M81" s="2" t="n">
         <v>94828.49000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3705-545-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>53063.75</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4281-188-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>33792.93</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5586-3645-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>36473.14</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4281-189-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>348.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2074,7 +2074,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2389-514-CM25</t>
+          <t>3477-493-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2114,17 +2114,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>33435.92</v>
+        <v>39448.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3477-493-CM25</t>
+          <t>2389-514-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2179,17 +2179,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>39448.4</v>
+        <v>33435.92</v>
       </c>
     </row>
     <row r="28">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2057-34-CM26</t>
+          <t>4281-60-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>75499.33</v>
+        <v>37938.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4281-60-CM26</t>
+          <t>2057-34-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>37938.64</v>
+        <v>75499.33</v>
       </c>
     </row>
     <row r="55">
@@ -4414,7 +4414,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3938-173-CM26</t>
+          <t>4993-261-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.265.000-k</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>38915.28</v>
+        <v>39707.27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4993-261-CM26</t>
+          <t>3938-173-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>39707.27</v>
+        <v>38915.28</v>
       </c>
     </row>
     <row r="64">
@@ -5117,7 +5117,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4118-31-CM26</t>
+          <t>4118-32-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5157,28 +5157,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>27195.83</v>
+        <v>59679.82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4118-32-CM26</t>
+          <t>4118-31-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5218,32 +5222,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>59679.82</v>
+        <v>27195.83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4177-100-CM26</t>
+          <t>4125-110-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5263,17 +5263,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>70.766.500-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5283,28 +5283,32 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>25368.27</v>
+        <v>38588.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4125-110-CM26</t>
+          <t>4177-100-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5324,17 +5328,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5344,26 +5348,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>38588.16</v>
+        <v>25368.27</v>
       </c>
     </row>
     <row r="77">
@@ -5816,7 +5816,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5586-3645-CM26</t>
+          <t>4281-189-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5856,17 +5856,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5875,13 +5875,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>36473.14</v>
+        <v>348.15</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4281-189-CM26</t>
+          <t>5586-3645-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5940,7 +5940,72 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>348.15</v>
+        <v>36473.14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2546-1021-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>9231.309999999999</v>
       </c>
     </row>
   </sheetData>
